--- a/Excel/Message.xlsx
+++ b/Excel/Message.xlsx
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="48.375" bestFit="1" customWidth="1"/>
@@ -817,6 +817,566 @@
       </c>
       <c r="D22" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>1021</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>업데이트 확인을 눌러 최신 정식 버전을 조회하세요.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Check for updates to find the latest stable version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>1022</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>최신 정식 버전을 확인하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Checking the latest stable version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>1023</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>현재 최신 정식 버전을 사용하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The application is up to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>1024</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>게시된 정식 릴리스가 없습니다.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No stable release is available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>1025</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>새 정식 버전 {0}을 설치할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Stable version {0} is available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>1026</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>자동 설치는 Windows x64 단일 실행 파일 배포에서 사용할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Automatic installation requires a published Windows x64 single executable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>1027</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>현재 앱의 버전 정보를 읽을 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>The current application version is invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>1028</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>업데이트 조회가 실패했습니다. 잠시 후 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>The update request failed. Try again later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>1029</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>공식 릴리스 정보를 사용할 수 없습니다. 릴리스 페이지를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>The official release information is invalid. Open the releases page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>1030</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>릴리스 파일에 SHA-256 정보가 없어 자동 설치할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>The release asset has no SHA-256 digest and cannot be installed automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>1031</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>업데이트 서버에 연결할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>The update service is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1032</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>이 릴리스에는 지원되는 단일 실행 파일이 없습니다. 릴리스 페이지를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>This release has no supported single executable. Open the releases page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1033</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>다운로드한 파일의 크기가 일치하지 않습니다. 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The downloaded file size does not match. Try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1034</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>업데이트 파일을 다운로드할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The update could not be downloaded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1035</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>다운로드한 파일의 SHA-256이 일치하지 않습니다. 설치하지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>The downloaded SHA-256 does not match. The update was not installed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1036</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>업데이트 설치를 준비할 수 없습니다. 파일 권한을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>The update could not be prepared. Check file permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1037</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>실행 파일 교체에 실패하여 기존 앱을 유지했습니다.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>The executable could not be replaced. The previous application was kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1038</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>기존 실행 파일 복원에 실패했습니다. 보존된 백업으로 복구하세요.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The previous executable could not be restored. Recover it from the retained backup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1039</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>정상 종료를 요청할 수 없습니다. 작업을 마친 뒤 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Normal shutdown is unavailable. Finish current work and try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1040</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>업데이트 다운로드 요청이 실패했습니다. 잠시 후 다시 시도하세요.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>The update download request failed. Try again later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1041</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>새 앱 실행에 실패하여 기존 실행 파일로 돌아왔습니다.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>The updated application could not be started. The previous executable was restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>1042</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>매크로 실행이나 입력 선택을 마친 뒤 업데이트하세요.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Finish macro execution or input selection before updating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>1043</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>업데이트 파일을 다운로드하고 확인하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Downloading and verifying the update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>1044</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>업데이트 후 재시작을 준비하는 중입니다.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Preparing to update and restart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>1045</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>정상 종료 후 업데이트하고 다시 시작합니다.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>The application will update and restart after normal shutdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>1046</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>업데이트 작업을 취소했습니다.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>The update operation was cancelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>1047</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>릴리스 페이지를 열 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The releases page could not be opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>1048</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>업데이트 작업을 완료하지 못했습니다. 로그를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>The update operation failed. Check the log for details.</t>
+        </is>
       </c>
     </row>
   </sheetData>
